--- a/diseases/d100/1985-1989.xlsx
+++ b/diseases/d100/1985-1989.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21933,7 +21933,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23933,7 +23933,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">

--- a/diseases/d100/1985-1989.xlsx
+++ b/diseases/d100/1985-1989.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21933,7 +21933,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23933,7 +23933,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
